--- a/src/cassy/additional_data/templates/path_config_template.xlsx
+++ b/src/cassy/additional_data/templates/path_config_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laghida\Documents\Github\cassy\src\cassy\additional_data\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3491EAC-79A1-4953-90B4-8FB184B3B827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFA7F1F-F48B-485C-B055-226AA750931A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-240" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-240" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Event Fatigue" sheetId="1" r:id="rId1"/>
@@ -126,9 +126,6 @@
     <t>Is Pressure</t>
   </si>
   <si>
-    <t>Is Occasional</t>
-  </si>
-  <si>
     <t>MPa</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
   </si>
   <si>
     <t>SS316L(N)-IG_SDC-IC</t>
+  </si>
+  <si>
+    <t>Is Short Overstress</t>
   </si>
 </sst>
 </file>
@@ -630,34 +630,34 @@
         <v>7</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -665,25 +665,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I2" s="9">
         <v>30000</v>
@@ -700,25 +700,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I3" s="9">
         <v>30000</v>
@@ -870,31 +870,31 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -902,25 +902,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
         <v>52</v>
       </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>54</v>
       </c>
       <c r="I2" s="3">
         <v>35</v>
@@ -934,25 +934,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
         <v>56</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>57</v>
       </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>58</v>
-      </c>
       <c r="H3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3">
         <v>35</v>
@@ -966,25 +966,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>52</v>
       </c>
-      <c r="F4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>54</v>
       </c>
       <c r="I4" s="3">
         <v>35</v>
@@ -998,25 +998,25 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
         <v>56</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="3">
         <v>35</v>
@@ -1079,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="J1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1087,28 +1087,28 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1116,28 +1116,28 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
         <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1145,10 +1145,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -1157,19 +1157,19 @@
         <v>0.33</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1177,10 +1177,10 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -1189,19 +1189,19 @@
         <v>0.33</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1209,10 +1209,10 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1221,19 +1221,19 @@
         <v>0.33</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="H6" t="s">
-        <v>38</v>
-      </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1364,7 +1364,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -1381,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>

--- a/src/cassy/additional_data/templates/path_config_template.xlsx
+++ b/src/cassy/additional_data/templates/path_config_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laghida\Documents\Github\cassy\src\cassy\additional_data\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFA7F1F-F48B-485C-B055-226AA750931A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEE6BE1-3DF8-4072-A1E9-38AE3DF68A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-240" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Event Fatigue" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,16 +235,36 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -259,11 +279,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -272,24 +307,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -306,6 +323,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -614,233 +660,237 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.3046875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.84375" customWidth="1"/>
-    <col min="3" max="4" width="25.84375" style="14" customWidth="1"/>
-    <col min="5" max="6" width="25.84375" style="15" customWidth="1"/>
-    <col min="7" max="8" width="25.84375" style="14" customWidth="1"/>
-    <col min="9" max="10" width="25.84375" style="13" customWidth="1"/>
-    <col min="11" max="11" width="25.84375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="19" style="7" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="25" style="8" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="15" style="8" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="16" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="9">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="3">
         <v>30000</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="3">
         <v>35</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="9">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="3">
         <v>30000</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="3">
         <v>35</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="9"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="9"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -853,73 +903,73 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.84375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="8" t="s">
         <v>53</v>
       </c>
       <c r="I2" s="3">
@@ -929,29 +979,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="8" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="3">
@@ -961,29 +1011,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="I4" s="3">
@@ -993,29 +1043,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="8" t="s">
         <v>53</v>
       </c>
       <c r="I5" s="3">
@@ -1036,203 +1086,203 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.53515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.69140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="16">
         <v>0.33</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="16">
         <v>0.33</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="16">
         <v>0.33</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1247,73 +1297,73 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3">
@@ -1331,39 +1381,39 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.3828125" customWidth="1"/>
-    <col min="4" max="5" width="13.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="8" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D2" s="3">
@@ -1373,14 +1423,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="3">
@@ -1401,19 +1451,19 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
@@ -1424,23 +1474,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="12" t="s">
         <v>4</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G4" t="s">
         <v>4</v>
       </c>
